--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_167_R17.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_167_R17.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7397</v>
+        <v>3.0559</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6762</v>
+        <v>3.9252</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9365</v>
+        <v>-0.8693</v>
       </c>
       <c r="G2" t="n">
         <v>-1.0611</v>
@@ -610,13 +610,13 @@
         <v>3.2473</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9478</v>
+        <v>1.2641</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5534</v>
+        <v>0.8024</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3945</v>
+        <v>0.4617</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3943</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. MONEKE</t>
+          <t>E. IZUNDU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9593</v>
+        <v>1.4668</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2855</v>
+        <v>1.3645</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3262</v>
+        <v>0.1023</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.8427</v>
+        <v>0.3468</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.9532</v>
+        <v>0.9423</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1105</v>
+        <v>-0.5955</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.5768</v>
+        <v>1.1795</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.9018</v>
+        <v>1.1427</v>
       </c>
       <c r="L3" t="n">
-        <v>1.325</v>
+        <v>0.0368</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.2659</v>
+        <v>-0.8327</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0514</v>
+        <v>-0.2004</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2144</v>
+        <v>-0.6323</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3792</v>
+        <v>0.4758</v>
       </c>
       <c r="T3" t="n">
-        <v>1.223</v>
+        <v>0.1849</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1562</v>
+        <v>0.2908</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5671</v>
+        <v>-0.2836</v>
       </c>
       <c r="W3" t="n">
-        <v>1.6393</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. IZUNDU</t>
+          <t>D. MOTIEJUNAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.628</v>
+        <v>0.8446</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5257</v>
+        <v>-0.2483</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1023</v>
+        <v>1.0929</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3468</v>
+        <v>0.5007</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9423</v>
+        <v>0.1861</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5955</v>
+        <v>0.3145</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1795</v>
+        <v>0.0504</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1427</v>
+        <v>0.0504</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0368</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8327</v>
+        <v>0.4502</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2004</v>
+        <v>0.1357</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6323</v>
+        <v>0.3145</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S4" t="n">
-        <v>0.637</v>
+        <v>-0.1199</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3462</v>
+        <v>-0.2987</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2908</v>
+        <v>0.1788</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. MOTIEJUNAS</t>
+          <t>C. MONEKE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8372000000000001</v>
+        <v>0.7378</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.323</v>
+        <v>1.5345</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1602</v>
+        <v>-0.7967</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5007</v>
+        <v>-2.8427</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1861</v>
+        <v>-2.9532</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3145</v>
+        <v>0.1105</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0504</v>
+        <v>-0.5768</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0504</v>
+        <v>-1.9018</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.325</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4502</v>
+        <v>-2.2659</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1357</v>
+        <v>-1.0514</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3145</v>
+        <v>-1.2144</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1274</v>
+        <v>1.1578</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3734</v>
+        <v>0.472</v>
       </c>
       <c r="U5" t="n">
-        <v>0.246</v>
+        <v>0.6858</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.5671</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.6393</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1468</v>
+        <v>0.4066</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.801</v>
+        <v>-0.6083</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9477</v>
+        <v>1.0149</v>
       </c>
       <c r="G6" t="n">
         <v>-2.1666</v>
@@ -922,13 +922,13 @@
         <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4577</v>
+        <v>0.7176</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0395</v>
+        <v>0.2322</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4182</v>
+        <v>0.4854</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1997</v>
+        <v>0.3969</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7217</v>
+        <v>-1.2932</v>
       </c>
       <c r="F7" t="n">
-        <v>1.522</v>
+        <v>1.6901</v>
       </c>
       <c r="G7" t="n">
         <v>-1.0981</v>
@@ -1000,13 +1000,13 @@
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2614</v>
+        <v>0.3352</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3734</v>
+        <v>0.0551</v>
       </c>
       <c r="U7" t="n">
-        <v>0.112</v>
+        <v>0.2801</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. MILJENOVIC</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2928</v>
+        <v>-0.0567</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8235</v>
+        <v>2.3035</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5306999999999999</v>
+        <v>-2.3602</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4401</v>
+        <v>4.0897</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6002</v>
+        <v>3.3068</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8399</v>
+        <v>0.783</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5223</v>
+        <v>8.153499999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7359</v>
+        <v>5.052</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7863</v>
+        <v>3.1015</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0822</v>
+        <v>-4.0638</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1357</v>
+        <v>-1.7452</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0535</v>
+        <v>-2.3186</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4639</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>2.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3888</v>
+        <v>0.753</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3734</v>
+        <v>0.2245</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0154</v>
+        <v>0.5285</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0722</v>
+        <v>-3.0438</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>-1.4355</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>S. MILJENOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3001</v>
+        <v>-0.1173</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9929</v>
+        <v>-0.7488</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.293</v>
+        <v>0.6315</v>
       </c>
       <c r="G9" t="n">
-        <v>4.0897</v>
+        <v>-1.4401</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3068</v>
+        <v>-0.6002</v>
       </c>
       <c r="I9" t="n">
-        <v>0.783</v>
+        <v>-0.8399</v>
       </c>
       <c r="J9" t="n">
-        <v>8.153499999999999</v>
+        <v>-1.5223</v>
       </c>
       <c r="K9" t="n">
-        <v>5.052</v>
+        <v>-0.7359</v>
       </c>
       <c r="L9" t="n">
-        <v>3.1015</v>
+        <v>-0.7863</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.0638</v>
+        <v>0.0822</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.7452</v>
+        <v>0.1357</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.3186</v>
+        <v>-0.0535</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7834</v>
+        <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5096000000000001</v>
+        <v>-0.2133</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0861</v>
+        <v>-0.2987</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5957</v>
+        <v>0.0854</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.0438</v>
+        <v>1.0722</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.4355</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4925</v>
+        <v>-0.9721</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0839</v>
+        <v>-0.4627</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4086</v>
+        <v>-0.5094</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1262</v>
@@ -1234,13 +1234,13 @@
         <v>2.3195</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2245</v>
+        <v>0.2959</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7978</v>
+        <v>-0.1766</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5733</v>
+        <v>0.4725</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9326</v>
+        <v>-1.8318</v>
       </c>
       <c r="E11" t="n">
         <v>0.2856</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2182</v>
+        <v>-2.1174</v>
       </c>
       <c r="G11" t="n">
         <v>-3.5211</v>
@@ -1312,13 +1312,13 @@
         <v>3.0154</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3412</v>
+        <v>1.442</v>
       </c>
       <c r="T11" t="n">
         <v>0.9243</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4169</v>
+        <v>0.5177</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6083</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8356</v>
+        <v>-2.9262</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1175</v>
+        <v>-1.4097</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7181</v>
+        <v>-1.5165</v>
       </c>
       <c r="G12" t="n">
         <v>0.0838</v>
@@ -1390,13 +1390,13 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3137</v>
+        <v>0.5957</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4481</v>
+        <v>0.2596</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1344</v>
+        <v>0.3361</v>
       </c>
       <c r="V12" t="n">
         <v>-1.7501</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2577000000000003</v>
+        <v>1.0045</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8953</v>
+        <v>4.6423</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.6377</v>
+        <v>-3.637799999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-8.2349</v>
@@ -1447,7 +1447,7 @@
         <v>10.7839</v>
       </c>
       <c r="L13" t="n">
-        <v>0.04889999999999994</v>
+        <v>0.0488999999999995</v>
       </c>
       <c r="M13" t="n">
         <v>-19.0677</v>
@@ -1468,13 +1468,13 @@
         <v>19.7159</v>
       </c>
       <c r="S13" t="n">
-        <v>5.9567</v>
+        <v>6.7039</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6342</v>
+        <v>2.381</v>
       </c>
       <c r="U13" t="n">
-        <v>4.3226</v>
+        <v>4.3228</v>
       </c>
       <c r="V13" t="n">
         <v>-5.582599999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. AKELE</t>
+          <t>L. VILDOZA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0564</v>
+        <v>4.2204</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2601</v>
+        <v>4.2711</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2038</v>
+        <v>-0.0506</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9315</v>
+        <v>5.0294</v>
       </c>
       <c r="H14" t="n">
-        <v>0.215</v>
+        <v>-0.0263</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7165</v>
+        <v>5.0557</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9862</v>
+        <v>6.3201</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1091</v>
+        <v>1.4151</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8771</v>
+        <v>4.905</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0547</v>
+        <v>-1.2907</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8942</v>
+        <v>-1.4414</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1605</v>
+        <v>0.1507</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1598</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9651</v>
+        <v>-0.1131</v>
       </c>
       <c r="T14" t="n">
-        <v>1.274</v>
+        <v>-0.8017</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3088</v>
+        <v>0.6886</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. VILDOZA</t>
+          <t>N. AKELE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7708</v>
+        <v>3.3772</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0352</v>
+        <v>3.4345</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2643</v>
+        <v>-0.0573</v>
       </c>
       <c r="G15" t="n">
-        <v>5.0294</v>
+        <v>1.9315</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0263</v>
+        <v>0.215</v>
       </c>
       <c r="I15" t="n">
-        <v>5.0557</v>
+        <v>1.7165</v>
       </c>
       <c r="J15" t="n">
-        <v>6.3201</v>
+        <v>2.9862</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4151</v>
+        <v>1.1091</v>
       </c>
       <c r="L15" t="n">
-        <v>4.905</v>
+        <v>1.8771</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2907</v>
+        <v>-1.0547</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4414</v>
+        <v>-0.8942</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1507</v>
+        <v>-0.1605</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5627</v>
+        <v>0.286</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0376</v>
+        <v>0.4483</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4749</v>
+        <v>-0.1623</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7117</v>
+        <v>2.9476</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2246</v>
+        <v>1.9887</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4871</v>
+        <v>0.9589</v>
       </c>
       <c r="G16" t="n">
         <v>2.3434</v>
@@ -1702,13 +1702,13 @@
         <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.405</v>
+        <v>-0.1691</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0272</v>
+        <v>-0.2631</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3778</v>
+        <v>0.094</v>
       </c>
       <c r="V16" t="n">
         <v>2.3969</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7035</v>
+        <v>2.4384</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4271</v>
+        <v>1.545</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2764</v>
+        <v>0.8934</v>
       </c>
       <c r="G17" t="n">
         <v>0.9865</v>
@@ -1780,13 +1780,13 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3552</v>
+        <v>-0.6203</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0376</v>
+        <v>-0.9197</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3176</v>
+        <v>0.2994</v>
       </c>
       <c r="V17" t="n">
         <v>1.6083</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8489</v>
+        <v>1.1102</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.2674</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1387</v>
+        <v>0.8428</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1463</v>
+        <v>-0.5702</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2185</v>
+        <v>-0.6037</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3648</v>
+        <v>0.0335</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0757</v>
+        <v>0.6418</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3396</v>
+        <v>0.605</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7361</v>
+        <v>0.0368</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9294</v>
+        <v>-1.212</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5581</v>
+        <v>-1.2087</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3713</v>
+        <v>-0.0033</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4639</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3804</v>
+        <v>-0.5052</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3655</v>
+        <v>-0.2869</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7459</v>
+        <v>-0.2183</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1418</v>
+        <v>2.6495</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1418</v>
+        <v>1.5773</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5154</v>
+        <v>0.6472</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0315</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4839</v>
+        <v>-0.063</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5702</v>
+        <v>0.1463</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6037</v>
+        <v>-0.2185</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0335</v>
+        <v>0.3648</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6418</v>
+        <v>1.0757</v>
       </c>
       <c r="K19" t="n">
-        <v>0.605</v>
+        <v>0.3396</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0368</v>
+        <v>0.7361</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.212</v>
+        <v>-0.9294</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2087</v>
+        <v>-0.5581</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0033</v>
+        <v>-0.3713</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4639</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1</v>
+        <v>0.1788</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5228</v>
+        <v>-0.3655</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5772</v>
+        <v>0.5443</v>
       </c>
       <c r="V19" t="n">
-        <v>2.6495</v>
+        <v>-0.1418</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.5773</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="20">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0025</v>
+        <v>-0.3849</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1515</v>
+        <v>0.0844</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.851</v>
+        <v>-0.4693</v>
       </c>
       <c r="G21" t="n">
         <v>1.5533</v>
@@ -2092,13 +2092,13 @@
         <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6669</v>
+        <v>-0.0492</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0376</v>
+        <v>-0.8017</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3708</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>2.2862</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2219</v>
+        <v>-1.1547</v>
       </c>
       <c r="E22" t="n">
         <v>-1.3302</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1083</v>
+        <v>0.1755</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0322</v>
@@ -2170,13 +2170,13 @@
         <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4938</v>
+        <v>-0.4266</v>
       </c>
       <c r="T22" t="n">
         <v>-0.224</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2697</v>
+        <v>-0.2025</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4354</v>
+        <v>-1.547</v>
       </c>
       <c r="E23" t="n">
         <v>-1.8683</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4329</v>
+        <v>0.3213</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5286999999999999</v>
@@ -2248,13 +2248,13 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4428</v>
+        <v>-0.5544</v>
       </c>
       <c r="T23" t="n">
         <v>-0.6721</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2293</v>
+        <v>0.1177</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9307</v>
+        <v>-3.6891</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0399</v>
+        <v>-0.922</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8907</v>
+        <v>-2.7671</v>
       </c>
       <c r="G24" t="n">
         <v>-1.5908</v>
@@ -2326,13 +2326,13 @@
         <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8913</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5926</v>
+        <v>-0.4689</v>
       </c>
       <c r="V24" t="n">
         <v>-2.1444</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.6999</v>
+        <v>-6.2902</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.6978</v>
+        <v>-4.5799</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0021</v>
+        <v>-1.7104</v>
       </c>
       <c r="G25" t="n">
         <v>-1.3849</v>
@@ -2404,13 +2404,13 @@
         <v>0.4639</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2274</v>
+        <v>-0.8178</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.854</v>
+        <v>-0.5623</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2576999999999989</v>
+        <v>2.1011</v>
       </c>
       <c r="E26" t="n">
-        <v>3.637800000000003</v>
+        <v>3.637700000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.8954</v>
+        <v>-1.5366</v>
       </c>
       <c r="G26" t="n">
         <v>8.2349</v>
@@ -2482,13 +2482,13 @@
         <v>11.5979</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.956900000000001</v>
+        <v>-3.5979</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.322500000000001</v>
+        <v>-4.322699999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.6341</v>
+        <v>0.7248999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>5.582500000000001</v>
